--- a/10_レビュー/レビュー記録_橋爪_2025.11.13.xlsx
+++ b/10_レビュー/レビュー記録_橋爪_2025.11.13.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HDC242310\Documents\卒業研究\仕様書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\sotsuken242310\10_レビュー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E892FD1A-6936-4915-838A-B102CC7EAFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295D7CA6-F7BA-4A24-B6F3-8261778EA6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7872" yWindow="2064" windowWidth="17172" windowHeight="10308" xr2:uid="{B5729C80-F964-450C-B0E5-72837C33B520}"/>
+    <workbookView xWindow="5325" yWindow="3465" windowWidth="21600" windowHeight="13965" xr2:uid="{B5729C80-F964-450C-B0E5-72837C33B520}"/>
   </bookViews>
   <sheets>
     <sheet name="レビュー記録" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
   <si>
     <t>参加者</t>
     <rPh sb="0" eb="3">
@@ -307,6 +307,40 @@
     </rPh>
     <rPh sb="4" eb="8">
       <t>ツイカヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>遷移図　流れ</t>
+    <rPh sb="0" eb="3">
+      <t>センイズ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メッセージ画面分離</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ブンリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フォロー中一覧</t>
+    <rPh sb="4" eb="7">
+      <t>チュウイチラン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ユーザーネームに変更</t>
+    <rPh sb="8" eb="10">
+      <t>ヘンコウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -740,28 +774,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3EC043C-8932-4DF6-AE1C-0E8E2671C937}">
   <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.09765625" customWidth="1"/>
-    <col min="2" max="2" width="7.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="56.19921875" customWidth="1"/>
+    <col min="1" max="1" width="3.125" customWidth="1"/>
+    <col min="2" max="2" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.25" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="56.19921875" customWidth="1"/>
+    <col min="5" max="5" width="56.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
@@ -769,7 +803,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B5" s="3" t="s">
         <v>0</v>
       </c>
@@ -777,8 +811,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
@@ -795,7 +829,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B8" s="2">
         <f>ROW()-7</f>
         <v>1</v>
@@ -813,7 +847,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B9" s="2">
         <f t="shared" ref="B9:B37" si="0">ROW()-7</f>
         <v>2</v>
@@ -831,7 +865,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B10" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -849,7 +883,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B11" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -867,7 +901,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B12" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -885,7 +919,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B13" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -903,7 +937,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B14" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -913,47 +947,55 @@
       <c r="E14" s="2"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B15" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="D15" s="4"/>
       <c r="E15" s="2"/>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B16" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C16" s="2"/>
+      <c r="C16" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="D16" s="4"/>
       <c r="E16" s="2"/>
       <c r="F16" s="4"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B17" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C17" s="2"/>
+      <c r="C17" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="D17" s="4"/>
       <c r="E17" s="2"/>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B18" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="D18" s="4"/>
       <c r="E18" s="2"/>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B19" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -963,7 +1005,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="4"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B20" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -973,7 +1015,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B21" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -983,7 +1025,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B22" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -993,7 +1035,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B23" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1003,7 +1045,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B24" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1013,7 +1055,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B25" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1023,7 +1065,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B26" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1033,7 +1075,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B27" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1043,7 +1085,7 @@
       <c r="E27" s="2"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B28" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1053,7 +1095,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B29" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1063,7 +1105,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B30" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1073,7 +1115,7 @@
       <c r="E30" s="2"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B31" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1083,7 +1125,7 @@
       <c r="E31" s="2"/>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B32" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -1093,7 +1135,7 @@
       <c r="E32" s="2"/>
       <c r="F32" s="4"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B33" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -1103,7 +1145,7 @@
       <c r="E33" s="2"/>
       <c r="F33" s="4"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B34" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -1113,7 +1155,7 @@
       <c r="E34" s="2"/>
       <c r="F34" s="4"/>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B35" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -1123,7 +1165,7 @@
       <c r="E35" s="2"/>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B36" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -1133,7 +1175,7 @@
       <c r="E36" s="2"/>
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B37" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1181,9 +1223,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EA7D3E-86FB-4487-9F7B-AFCD18575EFF}">
   <dimension ref="B2:D7"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1191,7 +1233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1199,7 +1241,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
@@ -1207,7 +1249,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1215,12 +1257,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
